--- a/artfynd/A 28535-2025 artfynd.xlsx
+++ b/artfynd/A 28535-2025 artfynd.xlsx
@@ -798,12 +798,7 @@
         <v>74269195</v>
       </c>
       <c r="B3" t="n">
-        <v>97050</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -835,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502448.4155016904</v>
+        <v>502448</v>
       </c>
       <c r="R3" t="n">
-        <v>6345783.976633099</v>
+        <v>6345784</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -868,19 +863,9 @@
           <t>1989-08-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1989-08-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 28535-2025 artfynd.xlsx
+++ b/artfynd/A 28535-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>74269195</v>
       </c>
       <c r="B3" t="n">
-        <v>99339</v>
+        <v>99344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28535-2025 artfynd.xlsx
+++ b/artfynd/A 28535-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>74269195</v>
       </c>
       <c r="B3" t="n">
-        <v>99344</v>
+        <v>99345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28535-2025 artfynd.xlsx
+++ b/artfynd/A 28535-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>74269195</v>
       </c>
       <c r="B3" t="n">
-        <v>99345</v>
+        <v>99372</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28535-2025 artfynd.xlsx
+++ b/artfynd/A 28535-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>74269195</v>
       </c>
       <c r="B3" t="n">
-        <v>99372</v>
+        <v>99378</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28535-2025 artfynd.xlsx
+++ b/artfynd/A 28535-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>74269195</v>
       </c>
       <c r="B3" t="n">
-        <v>99378</v>
+        <v>99385</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28535-2025 artfynd.xlsx
+++ b/artfynd/A 28535-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>74269195</v>
       </c>
       <c r="B3" t="n">
-        <v>99385</v>
+        <v>99389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28535-2025 artfynd.xlsx
+++ b/artfynd/A 28535-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>74269195</v>
       </c>
       <c r="B3" t="n">
-        <v>99389</v>
+        <v>99396</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28535-2025 artfynd.xlsx
+++ b/artfynd/A 28535-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>74269195</v>
       </c>
       <c r="B3" t="n">
-        <v>99399</v>
+        <v>99404</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28535-2025 artfynd.xlsx
+++ b/artfynd/A 28535-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>74269195</v>
       </c>
       <c r="B3" t="n">
-        <v>99404</v>
+        <v>99412</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28535-2025 artfynd.xlsx
+++ b/artfynd/A 28535-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>74269195</v>
       </c>
       <c r="B3" t="n">
-        <v>99412</v>
+        <v>99422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
